--- a/Convert_from_xlsx_to_Json/table_normalization/environment-table29.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/environment-table29.xlsx
@@ -135,8 +135,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="0.0%;[Red]\-0.0%"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0%;[Red]\-0.0%"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -325,26 +325,26 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -354,33 +354,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -388,6 +377,17 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1181,7 +1181,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" s="1" customFormat="1" ht="38.15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
       <c r="K1" s="15"/>
@@ -1190,16 +1190,16 @@
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="27" t="s">
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="25" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1207,21 +1207,21 @@
       <c r="A3" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="31"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="31"/>
+      <c r="K3" s="32"/>
     </row>
     <row r="4" spans="1:27" ht="75" customHeight="1">
-      <c r="A4" s="25"/>
+      <c r="A4" s="33"/>
       <c r="B4" s="5" t="s">
         <v>5</v>
       </c>
@@ -2070,7 +2070,7 @@
       <c r="AA20" s="20"/>
     </row>
     <row r="21" spans="1:27" ht="30" customHeight="1">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="27" t="s">
         <v>32</v>
       </c>
       <c r="B21" s="12">
